--- a/public/_fixtures/plan-thin.xlsx
+++ b/public/_fixtures/plan-thin.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="49">
   <si>
     <t>عنوان</t>
   </si>
@@ -62,6 +62,12 @@
     <t>البطولة القادمة</t>
   </si>
   <si>
+    <t>إجراءات الاستشفاء</t>
+  </si>
+  <si>
+    <t>إجراءات السلامة والوقاية</t>
+  </si>
+  <si>
     <t>م</t>
   </si>
   <si>
@@ -120,6 +126,9 @@
   </si>
   <si>
     <t>الراحة (د)</t>
+  </si>
+  <si>
+    <t>نوع المحتوى</t>
   </si>
   <si>
     <t>الأحد</t>
@@ -529,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -606,6 +615,22 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
         <v>8</v>
       </c>
     </row>
@@ -627,16 +652,16 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -644,7 +669,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
@@ -671,16 +696,16 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -688,7 +713,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
@@ -702,7 +727,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
@@ -719,7 +744,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -727,59 +752,62 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="K3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F4">
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -790,28 +818,31 @@
       <c r="J4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F5">
         <v>60</v>
       </c>
       <c r="G5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -822,28 +853,31 @@
       <c r="J5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F6">
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -854,28 +888,31 @@
       <c r="J6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
         <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F7">
         <v>60</v>
       </c>
       <c r="G7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -884,6 +921,9 @@
         <v>5</v>
       </c>
       <c r="J7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K7" t="s">
         <v>8</v>
       </c>
     </row>
@@ -905,19 +945,19 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
